--- a/recipes/Chamber-K 히터레시피 샘플.xlsx
+++ b/recipes/Chamber-K 히터레시피 샘플.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,23 +47,12 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -116,28 +105,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -503,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -512,10 +494,15 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>step</t>
@@ -547,6 +534,31 @@
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>use_ar</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ar_flow</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>use_o2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>o2_flow</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>wp_mtorr</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>예상 시간(분)</t>
         </is>
@@ -569,7 +581,24 @@
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" s="3">
         <f>IF(B2&lt;=30,E2,IF(D2&lt;&gt;"",D2,IF(IF(C2&lt;&gt;"",C2,12)&lt;=6,(ABS(B2-사용법!$C$3)/IF(C2&lt;&gt;"",C2,12)),((ABS(B2-사용법!$C$3)-MIN(ABS(B2-사용법!$C$3),10))/IF(C2&lt;&gt;"",C2,12)+MIN(ABS(B2-사용법!$C$3),10)/6)))+E2)</f>
         <v/>
       </c>
@@ -589,7 +618,12 @@
         <v>120</v>
       </c>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="3">
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="3">
         <f>IF(B3&lt;=30,E3,IF(D3&lt;&gt;"",D3,IF(IF(C3&lt;&gt;"",C3,12)&lt;=6,(ABS(B3-B2)/IF(C3&lt;&gt;"",C3,12)),((ABS(B3-B2)-MIN(ABS(B3-B2),10))/IF(C3&lt;&gt;"",C3,12)+MIN(ABS(B3-B2),10)/6)))+E3)</f>
         <v/>
       </c>
@@ -607,7 +641,12 @@
         <v>60</v>
       </c>
       <c r="F4" s="2" t="n"/>
-      <c r="G4" s="3">
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="3">
         <f>IF(B4&lt;=30,E4,IF(D4&lt;&gt;"",D4,IF(IF(C4&lt;&gt;"",C4,12)&lt;=6,(ABS(B4-B3)/IF(C4&lt;&gt;"",C4,12)),((ABS(B4-B3)-MIN(ABS(B4-B3),10))/IF(C4&lt;&gt;"",C4,12)+MIN(ABS(B4-B3),10)/6)))+E4)</f>
         <v/>
       </c>
@@ -623,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -639,478 +678,611 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>예상 시간(분) 열의 계산 기준</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>출발 온도(°C)</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>← 계산용 값입니다. 실제 제어와는 아무 상관이 없습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n"/>
-    </row>
+    </row>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>■ 이 파일이 하는 일</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t xml:space="preserve">   히터만 단독으로 운전하는 레시피입니다. 스퍼터 공정과 별개로 돌아갑니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t xml:space="preserve">   프로그램 히터 패널의 [레시피] 버튼으로 불러온 뒤 [시작] 을 누르면 실행됩니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t xml:space="preserve">   시트 이름은 'HeaterRecipe' 여야 합니다. 없으면 첫 번째 시트를 읽습니다.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="n"/>
-    </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>■ 컬럼</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t xml:space="preserve">   step             표시용 번호. 비워도 됩니다. '#' 으로 시작하면 그 줄은 주석으로 보고 건너뜁니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">   target_c         목표 온도 [°C]. 필수. 0 ~ 700 (config_user.json 의 HEATER_MAX_TEMP).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t xml:space="preserve">   ramp_c_per_min   승온 속도 [°C/min]. 비우면 기본값 12 를 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t xml:space="preserve">   ramp_min         승온에 걸릴 시간 [분]. 속도 대신 시간으로 지정할 때 씁니다 (PZ400 방식).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t xml:space="preserve">   soak_min         목표에 닿은 뒤 그 온도를 유지할 시간 [분]. 비우면 0.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t xml:space="preserve">   repeat           전체 패턴을 몇 번 돌릴지. 1~99. 비우면 1.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t xml:space="preserve">   예상 시간(분)     참고용 계산 열. 프로그램은 읽지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t xml:space="preserve">   ★ ramp_c_per_min 과 ramp_min 을 한 줄에 같이 쓰면 오류로 거부됩니다. 하나만 쓰세요.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t xml:space="preserve">   ★ repeat 은 첫 번째 데이터 행의 값만 읽습니다. 나머지 행의 repeat 는 무시됩니다.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="n"/>
-    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>■ 가스·압력 (선택) — 히터를 켜기 전에 가스를 넣고 압력을 잡는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   use_ar / ar_flow      Ar 사용 여부(T/F) · 유량 [sccm]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   use_o2 / o2_flow      O2 사용 여부(T/F) · 유량 [sccm]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   wp_mtorr              목표 압력 [mTorr]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ★ 첫 번째 데이터 행만 읽습니다. 레시피 전체에 하나입니다 (repeat 과 같은 규칙).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ★ 다섯 컬럼이 하나도 없으면 옛 레시피로 보고 패널의 가스·압력 설정을 그대로 씁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ★ 컬럼은 있는데 Ar/O2 둘 다 F 이면 '가스 안 씀'을 명시한 것입니다 — 진공에서 승온하고 압력도 잡지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>■ 가스를 쓰면 이렇게 진행됩니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1. 레시피를 불러오면 패널의 가스·압력 칸이 레시피 값으로 채워집니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2. [시작] 을 누르면 히터를 켜기 전에 MFC 가 순서대로 움직입니다:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Flow OFF → 메인밸브 Open → 영점 → 가스밸브 Open → 유량 설정·ON → SP1(목표 압력) 설정·ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      → 압력이 목표 ±10% 안에 3회 연속 들어오면 준비 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   3. 그때부터 1번 스텝 RAMP 가 시작됩니다. 패널 상태 라벨에 '준비중 n/m' → '준비됨' 으로 뜹니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   4. 준비 중 압력이 300초 안에 안 들어오면 실패로 보고 가스를 되돌립니다. 레시피는 시작하지 않습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   5. 레시피가 끝나거나 [정지] 를 눌러 히터가 꺼지면 가스도 자동으로 해제됩니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      (Flow OFF → 메인밸브 Open → 가스밸브 Close)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 스퍼터 공정과 달리 SP4·단계적 감압이 없습니다. 파워가 없어 곧바로 목표 압력으로 갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 스퍼터 공정과 순서가 반대입니다 — 공정은 고진공에서 승온한 뒤 가스를 넣지만, 여기서는 가스를 먼저 넣습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      영점(ZEROING)이 상온·가스 도입 전에 잡힙니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 가스가 잡혀 있는 동안에는 스퍼터 공정을 시작할 수 없습니다 (MFC 를 공유). 반대로 공정 중에는 히터 가스를 쓸 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 유량/압력이 벗어나면 경고(로그·구글챗)만 하고 히터는 끄지 않습니다 — 공정과 같은 정책입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>■ 한 스텝의 진행 — RAMP → SOAK, 두 단계뿐입니다</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t xml:space="preserve">   RAMP   램프 목표(SV)가 지정한 속도로 올라갑니다.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t xml:space="preserve">          SV 가 최종 목표에 닿는 순간 곧바로 SOAK 로 넘어갑니다.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t xml:space="preserve">          '도달 확인' 같은 중간 대기 단계는 없습니다 (2026-09-03 제거).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t xml:space="preserve">   SOAK   목표를 유지한 채 soak_min 분을 셉니다. 다 세면 다음 스텝으로.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t xml:space="preserve">   COOL   마지막 스텝의 target_c 가 30°C 이하이면 냉각 스텝으로 봅니다.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t xml:space="preserve">          히터는 식는 속도를 제어할 수 없으므로 램프 없이 soak_min 만 기다립니다.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t xml:space="preserve">          (중간 스텝에 낮은 온도를 쓰면 냉각 스텝이 아니라 일반 RAMP 로 처리됩니다)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t xml:space="preserve">   반복    repeat 이 2 이상이면 히터를 끄지 않고 그대로 1번 스텝으로 돌아갑니다.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t xml:space="preserve">   마지막   마지막 스텝이 끝나면 히터를 끕니다.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t xml:space="preserve">          (config_user.json 의 HEATER_RECIPE_HOLD_AT_END 를 true 로 두면 마지막 목표를 계속 유지합니다)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>■ 램프 속도 — 6°C/min 이 경계입니다</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t xml:space="preserve">   PLC 램프 생성기의 최소 단위가 1카운트/초 = 6°C/min 입니다.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t xml:space="preserve">   6 이상   6의 배수로 반올림해서 PLC 가 직접 램프를 만듭니다 (10 을 쓰면 12 가 됩니다).</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t xml:space="preserve">   6 미만   PLC 로는 표현되지 않으므로, 프로그램이 3초마다 목표를 조금씩 밀어 올려 만듭니다.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t xml:space="preserve">            (느린 램프). 값을 6 으로 올리지 않고 적은 그대로 실행합니다.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t xml:space="preserve">   목표 직전 10°C 구간은 오버슈트를 줄이려고 6°C/min 으로 낮춰 접근합니다.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t xml:space="preserve">   → 그래서 12°C/min 으로 275°C 를 올리면 산술값 22.9분이 아니라 약 23.8분이 걸립니다.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t xml:space="preserve">     오른쪽 '예상 시간(분)' 열은 이 저속 구간까지 넣어서 계산합니다.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>■ 실행 중 버튼</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t xml:space="preserve">   [레시피]     파일 불러오기 전용입니다. 실행 중에는 새 레시피를 불러올 수 없습니다.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t xml:space="preserve">   [시작]       불러온 레시피를 실행합니다.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t xml:space="preserve">   [일시정지]   진행 시계를 멈춥니다. 온도는 그대로 유지되고, 재개하면 멈춘 지점부터 이어집니다.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t xml:space="preserve">                일시정지 중에도 TC 단선·출력 이상 감시는 계속 돌아갑니다.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t xml:space="preserve">   [건너뛰기]   현재 스텝을 끝내고 다음 스텝으로 넘어갑니다.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t xml:space="preserve">   [정지]       히터 레시피만 중단합니다. 진행 중인 스퍼터 공정은 중단되지 않습니다.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+    <row r="73"/>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>■ 스퍼터 공정과 같이 돌릴 수 있습니다</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t xml:space="preserve">   히터 레시피가 온도를 쥔 채로 공정을 돌릴 수 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t xml:space="preserve">   단, 공정 레시피 쪽에서 use_heater = T 로 히터를 쓰면 그 공정이 히터의 주인이 되므로</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t xml:space="preserve">   히터 레시피와 같이 쓸 수 없습니다.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t xml:space="preserve">   → 히터 레시피로 온도를 유지하면서 공정을 돌리려면, 공정 레시피의</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t xml:space="preserve">     use_heater / heater_temp / heater_ramp 칸을 비워 두세요.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   단, 히터 레시피가 가스·압력을 쓰는 중이면 공정을 시작할 수 없습니다 (MFC 공유).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>■ 시간 초과 · 안전 감시</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t xml:space="preserve">   RAMP 타임아웃   스텝마다 따로 계산합니다. 예상 승온 시간 + 30분, 최소 90분, 최대 12시간.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t xml:space="preserve">                   넘기면 그 스텝에서 레시피를 중단합니다.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t xml:space="preserve">   TC 이상 60초 / 운전 중 DAC 출력 0 이 10초 / PLC RUN 꺼짐 5초 → 즉시 중단.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t xml:space="preserve">   중단되면 구글챗으로 사유가 담긴 알림이 갑니다.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="5" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+    <row r="87"/>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>■ 제한</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t xml:space="preserve">   최대 20 스텝 (HEATER_RECIPE_MAX_STEPS).</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t xml:space="preserve">   target_c 0 ~ 700°C · repeat 1 ~ 99 · soak_min 0 이상 · ramp_min 0 초과.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t xml:space="preserve">   레시피 시트에는 헤더와 데이터 행만 두세요. 합계·메모 행을 넣으면 로더가 오류를 냅니다.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t xml:space="preserve">   (메모를 남기려면 step 칸을 '#' 으로 시작하세요. 그 줄은 건너뜁니다)</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="5" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="9" t="inlineStr">
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>■ CSV 로도 됩니다</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t xml:space="preserve">   같은 컬럼명으로 UTF-8 CSV 를 만들어도 똑같이 동작합니다.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   step,target_c,ramp_c_per_min,ramp_min,soak_min,repeat</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>작성 2026-09-04 · 근거: 실측 데드타임 72초, 600°C 유지 MV 800 ≈ 59.8A, DAC 운전 상한 1200</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   step,target_c,ramp_c_per_min,ramp_min,soak_min,repeat,use_ar,ar_flow,use_o2,o2_flow,wp_mtorr</t>
+        </is>
+      </c>
+    </row>
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>작성 2026-09-07 · 근거: 실측 데드타임 72초, 600°C 유지 MV 800 ≈ 59.8A, DAC 운전 상한 1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>관련 설정: config_user.json 의 HEATER_* 항목 · PLC 래더 H6a(램프 생성기) · K1216~K1250(PID)</t>
         </is>

--- a/recipes/Chamber-K 히터레시피 샘플.xlsx
+++ b/recipes/Chamber-K 히터레시피 샘플.xlsx
@@ -678,7 +678,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -694,8 +693,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
@@ -713,7 +710,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   프로그램 히터 패널의 [레시피] 버튼으로 불러온 뒤 [시작] 을 누르면 실행됩니다.</t>
+          <t xml:space="preserve">   프로그램 히터 패널의 [레시피] 버튼으로 불러오면 스텝·분위기 확인창이 뜨고, 예를 누르면 바로 실행됩니다.</t>
         </is>
       </c>
     </row>
@@ -724,7 +721,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
@@ -742,7 +738,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   target_c         목표 온도 [°C]. 필수. 0 ~ 700 (config_user.json 의 HEATER_MAX_TEMP).</t>
+          <t xml:space="preserve">   target_c         목표 온도 [°C]. 필수. 0 ~ HEATER_MAX_TEMP (config_user.json, 현재 630).</t>
         </is>
       </c>
     </row>
@@ -795,7 +791,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -827,7 +822,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ★ 첫 번째 데이터 행만 읽습니다. 레시피 전체에 하나입니다 (repeat 과 같은 규칙).</t>
+          <t xml:space="preserve">   ★ repeat 과 같은 규칙으로 첫 번째 데이터 행만 읽습니다. 2행부터의 가스 칸은 무시되며, 레시피 전체(반복 포함)에 같은 가스·압력이 유지됩니다. 첫 행의 가스 칸을 비우면 F 로 봅니다.</t>
         </is>
       </c>
     </row>
@@ -845,7 +840,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
@@ -884,7 +878,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   3. 그때부터 1번 스텝 RAMP 가 시작됩니다. 패널 상태 라벨에 '준비중 n/m' → '준비됨' 으로 뜹니다</t>
+          <t xml:space="preserve">   3. 그때부터 1번 스텝 RAMP 가 시작됩니다. 준비 중에는 상태 문구에 '가스 준비중 n/m' 이 뜨고 ON 버튼이 [취소] 가 됩니다. 준비가 끝나면 '운전 중' 으로 바뀝니다</t>
         </is>
       </c>
     </row>
@@ -898,7 +892,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5. 레시피가 끝나거나 [정지] 를 눌러 히터가 꺼지면 가스도 자동으로 해제됩니다</t>
+          <t xml:space="preserve">   5. 레시피가 끝나거나 [정지] 로 히터가 꺼져도 PV 가 100°C(HEATER_GAS_HOLD_RELEASE_C) 이하로 식을 때까지 가스·압력을 유지합니다('가스 유지 · 냉각 중'). 그 아래로 내려가면 자동 해제되고, 먼저 끊으려면 [가스 해제] 버튼을 누릅니다. 유지 중에 공정 Start 를 누르면 해제하고 시작할지 묻습니다</t>
         </is>
       </c>
     </row>
@@ -944,7 +938,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
@@ -1022,7 +1015,6 @@
         </is>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
@@ -1079,7 +1071,6 @@
         </is>
       </c>
     </row>
-    <row r="65"/>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
@@ -1129,7 +1120,6 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
@@ -1179,7 +1169,6 @@
         </is>
       </c>
     </row>
-    <row r="81"/>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
@@ -1215,7 +1204,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
@@ -1251,7 +1239,6 @@
         </is>
       </c>
     </row>
-    <row r="93"/>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
@@ -1273,7 +1260,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>

--- a/recipes/Chamber-K 히터레시피 샘플.xlsx
+++ b/recipes/Chamber-K 히터레시피 샘플.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -493,13 +493,12 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,35 +529,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>repeat</t>
+          <t>use_ar</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>use_ar</t>
+          <t>ar_flow</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>ar_flow</t>
+          <t>use_o2</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>use_o2</t>
+          <t>o2_flow</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>o2_flow</t>
+          <t>wp_mtorr</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>wp_mtorr</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>예상 시간(분)</t>
         </is>
@@ -578,28 +572,25 @@
       <c r="E2" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n">
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L2" s="3">
-        <f>IF(B2&lt;=30,E2,IF(D2&lt;&gt;"",D2,IF(IF(C2&lt;&gt;"",C2,12)&lt;=6,(ABS(B2-사용법!$C$3)/IF(C2&lt;&gt;"",C2,12)),((ABS(B2-사용법!$C$3)-MIN(ABS(B2-사용법!$C$3),10))/IF(C2&lt;&gt;"",C2,12)+MIN(ABS(B2-사용법!$C$3),10)/6)))+E2)</f>
+      <c r="K2" s="3">
+        <f>IF(B2&lt;=30,E2,IF(D2&lt;&gt;"",D2,IF(OR(IF(C2&lt;&gt;"",C2,12)&lt;=사용법!$G$3,사용법!$E$3&lt;=0),ABS(B2-사용법!$C$3)/IF(C2&lt;&gt;"",C2,12),(ABS(B2-사용법!$C$3)-MIN(ABS(B2-사용법!$C$3),사용법!$E$3))/IF(C2&lt;&gt;"",C2,12)+LN((사용법!$G$3+(IF(C2&lt;&gt;"",C2,12)-사용법!$G$3)*MIN(ABS(B2-사용법!$C$3),사용법!$E$3)/사용법!$E$3)/사용법!$G$3)*사용법!$E$3/(IF(C2&lt;&gt;"",C2,12)-사용법!$G$3)))+E2)</f>
         <v/>
       </c>
     </row>
@@ -622,9 +613,8 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="3">
-        <f>IF(B3&lt;=30,E3,IF(D3&lt;&gt;"",D3,IF(IF(C3&lt;&gt;"",C3,12)&lt;=6,(ABS(B3-B2)/IF(C3&lt;&gt;"",C3,12)),((ABS(B3-B2)-MIN(ABS(B3-B2),10))/IF(C3&lt;&gt;"",C3,12)+MIN(ABS(B3-B2),10)/6)))+E3)</f>
+      <c r="K3" s="3">
+        <f>IF(B3&lt;=30,E3,IF(D3&lt;&gt;"",D3,IF(OR(IF(C3&lt;&gt;"",C3,12)&lt;=사용법!$G$3,사용법!$E$3&lt;=0),ABS(B3-B2)/IF(C3&lt;&gt;"",C3,12),(ABS(B3-B2)-MIN(ABS(B3-B2),사용법!$E$3))/IF(C3&lt;&gt;"",C3,12)+LN((사용법!$G$3+(IF(C3&lt;&gt;"",C3,12)-사용법!$G$3)*MIN(ABS(B3-B2),사용법!$E$3)/사용법!$E$3)/사용법!$G$3)*사용법!$E$3/(IF(C3&lt;&gt;"",C3,12)-사용법!$G$3)))+E3)</f>
         <v/>
       </c>
     </row>
@@ -645,9 +635,8 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="3">
-        <f>IF(B4&lt;=30,E4,IF(D4&lt;&gt;"",D4,IF(IF(C4&lt;&gt;"",C4,12)&lt;=6,(ABS(B4-B3)/IF(C4&lt;&gt;"",C4,12)),((ABS(B4-B3)-MIN(ABS(B4-B3),10))/IF(C4&lt;&gt;"",C4,12)+MIN(ABS(B4-B3),10)/6)))+E4)</f>
+      <c r="K4" s="3">
+        <f>IF(B4&lt;=30,E4,IF(D4&lt;&gt;"",D4,IF(OR(IF(C4&lt;&gt;"",C4,12)&lt;=사용법!$G$3,사용법!$E$3&lt;=0),ABS(B4-B3)/IF(C4&lt;&gt;"",C4,12),(ABS(B4-B3)-MIN(ABS(B4-B3),사용법!$E$3))/IF(C4&lt;&gt;"",C4,12)+LN((사용법!$G$3+(IF(C4&lt;&gt;"",C4,12)-사용법!$G$3)*MIN(ABS(B4-B3),사용법!$E$3)/사용법!$E$3)/사용법!$G$3)*사용법!$E$3/(IF(C4&lt;&gt;"",C4,12)-사용법!$G$3)))+E4)</f>
         <v/>
       </c>
     </row>
@@ -662,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C99"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -692,6 +681,22 @@
       <c r="C3" s="6" t="n">
         <v>25</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>접근 구간(°C)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>최저 접근 속도(°C/min)</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -766,509 +771,482 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   repeat           전체 패턴을 몇 번 돌릴지. 1~99. 비우면 1.</t>
+          <t xml:space="preserve">   예상 시간(분)     참고용 계산 열. 프로그램은 읽지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   예상 시간(분)     참고용 계산 열. 프로그램은 읽지 않습니다.</t>
+          <t xml:space="preserve">   ★ ramp_c_per_min 과 ramp_min 을 한 줄에 같이 쓰면 오류로 거부됩니다. 하나만 쓰세요.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ★ ramp_c_per_min 과 ramp_min 을 한 줄에 같이 쓰면 오류로 거부됩니다. 하나만 쓰세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ★ repeat 은 첫 번째 데이터 행의 값만 읽습니다. 나머지 행의 repeat 는 무시됩니다.</t>
+          <t xml:space="preserve">   ★ 반복 기능은 없습니다. 같은 스텝을 여러 번 돌리려면 행을 복사해서 이어 적으세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>■ 가스·압력 (선택) — 히터를 켜기 전에 가스를 넣고 압력을 잡는다</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>■ 가스·압력 (선택) — 히터를 켜기 전에 가스를 넣고 압력을 잡는다</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   use_ar / ar_flow      Ar 사용 여부(T/F) · 유량 [sccm]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   use_ar / ar_flow      Ar 사용 여부(T/F) · 유량 [sccm]</t>
+          <t xml:space="preserve">   use_o2 / o2_flow      O2 사용 여부(T/F) · 유량 [sccm]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   use_o2 / o2_flow      O2 사용 여부(T/F) · 유량 [sccm]</t>
+          <t xml:space="preserve">   wp_mtorr              목표 압력 [mTorr]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">   wp_mtorr              목표 압력 [mTorr]</t>
+          <t xml:space="preserve">   ★ 첫 번째 데이터 행만 읽습니다. 2행부터의 가스 칸은 무시되며 레시피 전체에 같은 가스·압력이 유지됩니다. 첫 행의 가스 칸을 비우면 F 로 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ★ repeat 과 같은 규칙으로 첫 번째 데이터 행만 읽습니다. 2행부터의 가스 칸은 무시되며, 레시피 전체(반복 포함)에 같은 가스·압력이 유지됩니다. 첫 행의 가스 칸을 비우면 F 로 봅니다.</t>
+          <t xml:space="preserve">   ★ 다섯 컬럼이 하나도 없으면 옛 레시피로 보고 패널의 가스·압력 설정을 그대로 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ★ 다섯 컬럼이 하나도 없으면 옛 레시피로 보고 패널의 가스·압력 설정을 그대로 씁니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
           <t xml:space="preserve">   ★ 컬럼은 있는데 Ar/O2 둘 다 F 이면 '가스 안 씀'을 명시한 것입니다 — 진공에서 승온하고 압력도 잡지 않습니다.</t>
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>■ 가스를 쓰면 이렇게 진행됩니다</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>■ 가스를 쓰면 이렇게 진행됩니다</t>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1. 레시피를 불러오면 패널의 가스·압력 칸이 레시피 값으로 채워집니다</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1. 레시피를 불러오면 패널의 가스·압력 칸이 레시피 값으로 채워집니다</t>
+          <t xml:space="preserve">   2. 확인창에서 예를 누르면 히터를 켜기 전에 MFC 가 순서대로 움직입니다:</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   2. [시작] 을 누르면 히터를 켜기 전에 MFC 가 순서대로 움직입니다:</t>
+          <t xml:space="preserve">      Flow OFF → 메인밸브 Open → 영점 → 가스밸브 Open → 유량 설정·ON → SP1(목표 압력) 설정·ON</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Flow OFF → 메인밸브 Open → 영점 → 가스밸브 Open → 유량 설정·ON → SP1(목표 압력) 설정·ON</t>
+          <t xml:space="preserve">      → 압력이 목표 ±10% 안에 3회 연속 들어오면 준비 완료</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">      → 압력이 목표 ±10% 안에 3회 연속 들어오면 준비 완료</t>
+          <t xml:space="preserve">   3. 그때부터 1번 스텝 RAMP 가 시작됩니다. 준비 중에는 상태 문구에 '가스 준비중 n/m' 이 뜨고 ON 버튼이 [취소] 가 됩니다. 준비가 끝나면 '운전 중' 으로 바뀝니다</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   3. 그때부터 1번 스텝 RAMP 가 시작됩니다. 준비 중에는 상태 문구에 '가스 준비중 n/m' 이 뜨고 ON 버튼이 [취소] 가 됩니다. 준비가 끝나면 '운전 중' 으로 바뀝니다</t>
+          <t xml:space="preserve">   4. 준비 중 압력이 300초 안에 안 들어오면 실패로 보고 가스를 되돌립니다. 레시피는 시작하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4. 준비 중 압력이 300초 안에 안 들어오면 실패로 보고 가스를 되돌립니다. 레시피는 시작하지 않습니다</t>
+          <t xml:space="preserve">   5. 레시피가 끝나거나 [정지] 로 히터가 꺼져도 PV 가 100°C(HEATER_GAS_HOLD_RELEASE_C) 이하로 식을 때까지 가스·압력을 유지합니다('가스 유지 · 냉각 중'). 그 아래로 내려가면 자동 해제되고, 먼저 끊으려면 [가스 해제] 버튼을 누릅니다. 유지 중에 공정 Start 를 누르면 해제하고 시작할지 묻습니다</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5. 레시피가 끝나거나 [정지] 로 히터가 꺼져도 PV 가 100°C(HEATER_GAS_HOLD_RELEASE_C) 이하로 식을 때까지 가스·압력을 유지합니다('가스 유지 · 냉각 중'). 그 아래로 내려가면 자동 해제되고, 먼저 끊으려면 [가스 해제] 버튼을 누릅니다. 유지 중에 공정 Start 를 누르면 해제하고 시작할지 묻습니다</t>
+          <t xml:space="preserve">      (Flow OFF → 메인밸브 Open → 가스밸브 Close)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">      (Flow OFF → 메인밸브 Open → 가스밸브 Close)</t>
+          <t xml:space="preserve">   ※ 스퍼터 공정과 달리 SP4·단계적 감압이 없습니다. 파워가 없어 곧바로 목표 압력으로 갑니다.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ※ 스퍼터 공정과 달리 SP4·단계적 감압이 없습니다. 파워가 없어 곧바로 목표 압력으로 갑니다.</t>
+          <t xml:space="preserve">   ※ 스퍼터 공정과 순서가 반대입니다 — 공정은 고진공에서 승온한 뒤 가스를 넣지만, 여기서는 가스를 먼저 넣습니다.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ※ 스퍼터 공정과 순서가 반대입니다 — 공정은 고진공에서 승온한 뒤 가스를 넣지만, 여기서는 가스를 먼저 넣습니다.</t>
+          <t xml:space="preserve">      영점(ZEROING)이 상온·가스 도입 전에 잡힙니다.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">      영점(ZEROING)이 상온·가스 도입 전에 잡힙니다.</t>
+          <t xml:space="preserve">   ※ 가스가 잡혀 있는 동안에는 스퍼터 공정을 시작할 수 없습니다 (MFC 를 공유). 반대로 공정 중에는 히터 가스를 쓸 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ※ 가스가 잡혀 있는 동안에는 스퍼터 공정을 시작할 수 없습니다 (MFC 를 공유). 반대로 공정 중에는 히터 가스를 쓸 수 없습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
           <t xml:space="preserve">   ※ 유량/압력이 벗어나면 경고(로그·구글챗)만 하고 히터는 끄지 않습니다 — 공정과 같은 정책입니다.</t>
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>■ 한 스텝의 진행 — RAMP → SOAK, 두 단계뿐입니다</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>■ 한 스텝의 진행 — RAMP → SOAK, 두 단계뿐입니다</t>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   RAMP   램프 목표(SV)가 지정한 속도로 올라갑니다.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">   RAMP   램프 목표(SV)가 지정한 속도로 올라갑니다.</t>
+          <t xml:space="preserve">          SV 가 최종 목표에 닿는 순간 곧바로 SOAK 로 넘어갑니다.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">          SV 가 최종 목표에 닿는 순간 곧바로 SOAK 로 넘어갑니다.</t>
+          <t xml:space="preserve">          '도달 확인' 같은 중간 대기 단계는 없습니다 (2026-09-03 제거).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">          '도달 확인' 같은 중간 대기 단계는 없습니다 (2026-09-03 제거).</t>
+          <t xml:space="preserve">   SOAK   목표를 유지한 채 soak_min 분을 셉니다. 다 세면 다음 스텝으로.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">   SOAK   목표를 유지한 채 soak_min 분을 셉니다. 다 세면 다음 스텝으로.</t>
+          <t xml:space="preserve">   COOL   마지막 스텝의 target_c 가 30°C 이하이면 냉각 스텝으로 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   COOL   마지막 스텝의 target_c 가 30°C 이하이면 냉각 스텝으로 봅니다.</t>
+          <t xml:space="preserve">          히터는 식는 속도를 제어할 수 없으므로 램프 없이 soak_min 만 기다립니다.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">          히터는 식는 속도를 제어할 수 없으므로 램프 없이 soak_min 만 기다립니다.</t>
+          <t xml:space="preserve">          (중간 스텝에 낮은 온도를 쓰면 냉각 스텝이 아니라 일반 RAMP 로 처리됩니다)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">          (중간 스텝에 낮은 온도를 쓰면 냉각 스텝이 아니라 일반 RAMP 로 처리됩니다)</t>
+          <t xml:space="preserve">   마지막   마지막 스텝이 끝나면 히터를 끕니다.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">   반복    repeat 이 2 이상이면 히터를 끄지 않고 그대로 1번 스텝으로 돌아갑니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   마지막   마지막 스텝이 끝나면 히터를 끕니다.</t>
+          <t xml:space="preserve">          (config_user.json 의 HEATER_RECIPE_HOLD_AT_END 를 true 로 두면 마지막 목표를 계속 유지합니다)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          (config_user.json 의 HEATER_RECIPE_HOLD_AT_END 를 true 로 두면 마지막 목표를 계속 유지합니다)</t>
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>■ 램프 속도와 목표 접근</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   프로그램이 1초마다 목표(SV)를 조금씩 밀어 올려 램프를 만듭니다. 6°C/min 미만이나 6의 배수가 아닌 속도도 적은 그대로 실행됩니다.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>■ 램프 속도 — 6°C/min 이 경계입니다</t>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   목표 직전 접근 구간(위 E3, 현재 20°C)에서는 남은 거리에 비례해 속도를 줄여 최저 접근 속도(위 G3, 현재 1°C/min)로 도착합니다.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">   PLC 램프 생성기의 최소 단위가 1카운트/초 = 6°C/min 입니다.</t>
+          <t xml:space="preserve">   → 도착 순간 히터에 남는 잉여 전력이 작아져 오버슈트가 줄어듭니다. (config_user.json 의 HEATER_APPROACH_ZONE_C / HEATER_APPROACH_MIN_RATE_C_PER_MIN)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">   6 이상   6의 배수로 반올림해서 PLC 가 직접 램프를 만듭니다 (10 을 쓰면 12 가 됩니다).</t>
+          <t xml:space="preserve">   ramp_c_per_min 은 접근 구간 전까지의 속도이고, ramp_min 은 접근 구간까지 포함한 전체 시간입니다(그 시간에 맞게 본 구간 속도를 역산합니다).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">   6 미만   PLC 로는 표현되지 않으므로, 프로그램이 3초마다 목표를 조금씩 밀어 올려 만듭니다.</t>
+          <t xml:space="preserve">   → 그래서 12°C/min 으로 275°C 를 올리면 산술값 22.9분이 아니라 약 25.8분이 걸립니다.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">            (느린 램프). 값을 6 으로 올리지 않고 적은 그대로 실행합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   목표 직전 10°C 구간은 오버슈트를 줄이려고 6°C/min 으로 낮춰 접근합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → 그래서 12°C/min 으로 275°C 를 올리면 산술값 22.9분이 아니라 약 23.8분이 걸립니다.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">     오른쪽 '예상 시간(분)' 열은 이 접근 구간까지 넣어서 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     오른쪽 '예상 시간(분)' 열은 이 저속 구간까지 넣어서 계산합니다.</t>
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>■ 실행 중 버튼</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   [레시피]     파일을 불러와 스텝·분위기 확인창을 띄우고, 예를 누르면 바로 실행합니다. 실행 중에는 누를 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>■ 실행 중 버튼</t>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   [일시정지]   진행 시계를 멈춥니다. 온도는 그대로 유지되고, 재개하면 멈춘 지점부터 이어집니다.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">   [레시피]     파일 불러오기 전용입니다. 실행 중에는 새 레시피를 불러올 수 없습니다.</t>
+          <t xml:space="preserve">                일시정지 중에도 TC 단선·출력 이상 감시는 계속 돌아갑니다.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">   [시작]       불러온 레시피를 실행합니다.</t>
+          <t xml:space="preserve">   [건너뛰기]   현재 스텝을 끝내고 다음 스텝으로 넘어갑니다.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">   [일시정지]   진행 시계를 멈춥니다. 온도는 그대로 유지되고, 재개하면 멈춘 지점부터 이어집니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                일시정지 중에도 TC 단선·출력 이상 감시는 계속 돌아갑니다.</t>
+          <t xml:space="preserve">   [정지]       히터 레시피만 중단합니다. 진행 중인 스퍼터 공정은 중단되지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   [건너뛰기]   현재 스텝을 끝내고 다음 스텝으로 넘어갑니다.</t>
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>■ 스퍼터 공정과 같이 돌릴 수 있습니다</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">   [정지]       히터 레시피만 중단합니다. 진행 중인 스퍼터 공정은 중단되지 않습니다.</t>
+          <t xml:space="preserve">   히터 레시피가 온도를 쥔 채로 공정을 돌릴 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   단, 공정 레시피 쪽에서 use_heater = T 로 히터를 쓰면 그 공정이 히터의 주인이 되므로</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>■ 스퍼터 공정과 같이 돌릴 수 있습니다</t>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   히터 레시피와 같이 쓸 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">   히터 레시피가 온도를 쥔 채로 공정을 돌릴 수 있습니다.</t>
+          <t xml:space="preserve">   → 히터 레시피로 온도를 유지하면서 공정을 돌리려면, 공정 레시피의</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">   단, 공정 레시피 쪽에서 use_heater = T 로 히터를 쓰면 그 공정이 히터의 주인이 되므로</t>
+          <t xml:space="preserve">     use_heater / heater_temp / heater_ramp 칸을 비워 두세요.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">   히터 레시피와 같이 쓸 수 없습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → 히터 레시피로 온도를 유지하면서 공정을 돌리려면, 공정 레시피의</t>
+          <t xml:space="preserve">   단, 히터 레시피가 가스·압력을 쓰는 중이면 공정을 시작할 수 없습니다 (MFC 공유).</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     use_heater / heater_temp / heater_ramp 칸을 비워 두세요.</t>
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>■ 시간 초과 · 안전 감시</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">   단, 히터 레시피가 가스·압력을 쓰는 중이면 공정을 시작할 수 없습니다 (MFC 공유).</t>
+          <t xml:space="preserve">   RAMP 타임아웃   스텝마다 따로 계산합니다. 예상 승온 시간 + 30분, 최소 90분, 최대 12시간.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                   넘기면 그 스텝에서 레시피를 중단합니다.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>■ 시간 초과 · 안전 감시</t>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   TC 이상 60초 / 운전 중 DAC 출력 0 이 10초 / PLC RUN 꺼짐 5초 → 즉시 중단.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">   RAMP 타임아웃   스텝마다 따로 계산합니다. 예상 승온 시간 + 30분, 최소 90분, 최대 12시간.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   넘기면 그 스텝에서 레시피를 중단합니다.</t>
+          <t xml:space="preserve">   중단되면 구글챗으로 사유가 담긴 알림이 갑니다.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   TC 이상 60초 / 운전 중 DAC 출력 0 이 10초 / PLC RUN 꺼짐 5초 → 즉시 중단.</t>
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>■ 제한</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">   중단되면 구글챗으로 사유가 담긴 알림이 갑니다.</t>
+          <t xml:space="preserve">   최대 20 스텝 (HEATER_RECIPE_MAX_STEPS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   target_c 0 ~ HEATER_MAX_TEMP · soak_min 0 이상 · ramp_min 0 초과.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>■ 제한</t>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   레시피 시트에는 헤더와 데이터 행만 두세요. 합계·메모 행을 넣으면 로더가 오류를 냅니다.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">   최대 20 스텝 (HEATER_RECIPE_MAX_STEPS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   target_c 0 ~ 700°C · repeat 1 ~ 99 · soak_min 0 이상 · ramp_min 0 초과.</t>
+          <t xml:space="preserve">   (메모를 남기려면 step 칸을 '#' 으로 시작하세요. 그 줄은 건너뜁니다)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   레시피 시트에는 헤더와 데이터 행만 두세요. 합계·메모 행을 넣으면 로더가 오류를 냅니다.</t>
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>■ CSV 로도 됩니다</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (메모를 남기려면 step 칸을 '#' 으로 시작하세요. 그 줄은 건너뜁니다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>■ CSV 로도 됩니다</t>
+          <t xml:space="preserve">   같은 컬럼명으로 UTF-8 CSV 를 만들어도 똑같이 동작합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   step,target_c,ramp_c_per_min,ramp_min,soak_min,use_ar,ar_flow,use_o2,o2_flow,wp_mtorr</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">   같은 컬럼명으로 UTF-8 CSV 를 만들어도 똑같이 동작합니다.</t>
+          <t>작성 2026-09-07 · 근거: 실측 데드타임 72초, 600°C 유지 MV 800 ≈ 59.8A, DAC 운전 상한 1200</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   step,target_c,ramp_c_per_min,ramp_min,soak_min,repeat,use_ar,ar_flow,use_o2,o2_flow,wp_mtorr</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>작성 2026-09-07 · 근거: 실측 데드타임 72초, 600°C 유지 MV 800 ≈ 59.8A, DAC 운전 상한 1200</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
         <is>
           <t>관련 설정: config_user.json 의 HEATER_* 항목 · PLC 래더 H6a(램프 생성기) · K1216~K1250(PID)</t>
         </is>
